--- a/data/samples/DEMO01.xlsx
+++ b/data/samples/DEMO01.xlsx
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>30500</v>
+        <v>29836</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>18300</v>
+        <v>17902</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>32500</v>
+        <v>33164</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>16775</v>
+        <v>16410</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>31000</v>
+        <v>29362</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>18600</v>
+        <v>17617</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>35000</v>
+        <v>36638</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>17050</v>
+        <v>16149</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
